--- a/src/Scenario 2_care_gap_multi_measure_dataset.xlsx
+++ b/src/Scenario 2_care_gap_multi_measure_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2416789_cognizant_com1/Documents/Desktop/Knowledge-GraphTesting/Knowledge-Graph-AIAgent/src/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="518" documentId="13_ncr:1_{EBCA80F7-FBA1-4C12-9752-7625893357B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B79E715-2272-48E9-86E8-6DE760559A69}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AC5525-03B3-4EC0-A8A4-19DB22122413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="905" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -37,8 +37,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1594,20 +1592,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" customWidth="1"/>
-    <col min="3" max="3" width="21.36328125" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" customWidth="1"/>
-    <col min="6" max="6" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.21875" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1636,7 +1634,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1663,10 +1661,10 @@
       </c>
       <c r="I2" s="20" t="str">
         <f ca="1">DATEDIF(C2, TODAY(), "Y") &amp; " Years, " &amp; DATEDIF(C2, TODAY(), "YM") &amp; " Months"</f>
-        <v>34 Years, 8 Months</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+        <v>34 Years, 9 Months</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1696,7 +1694,7 @@
         <v>41 Years, 6 Months</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1723,10 +1721,10 @@
       </c>
       <c r="I4" s="20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>47 Years, 11 Months</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+        <v>48 Years, 0 Months</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1756,7 +1754,7 @@
         <v>69 Years, 7 Months</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1786,7 +1784,7 @@
         <v>58 Years, 9 Months</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1816,7 +1814,7 @@
         <v>63 Years, 4 Months</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1846,7 +1844,7 @@
         <v>35 Years, 5 Months</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1876,7 +1874,7 @@
         <v>61 Years, 3 Months</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1906,7 +1904,7 @@
         <v>71 Years, 10 Months</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1936,7 +1934,7 @@
         <v>73 Years, 5 Months</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>48</v>
       </c>
@@ -1963,10 +1961,10 @@
       </c>
       <c r="I12" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>42 Years, 4 Months</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>42 Years, 5 Months</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -1996,7 +1994,7 @@
         <v>41 Years, 0 Months</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -2026,7 +2024,7 @@
         <v>36 Years, 0 Months</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -2056,7 +2054,7 @@
         <v>39 Years, 7 Months</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -2083,10 +2081,10 @@
       </c>
       <c r="I16" s="20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>53 Years, 10 Months</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+        <v>53 Years, 11 Months</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -2116,7 +2114,7 @@
         <v>28 Years, 10 Months</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -2146,7 +2144,7 @@
         <v>54 Years, 9 Months</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -2176,7 +2174,7 @@
         <v>24 Years, 3 Months</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -2203,10 +2201,10 @@
       </c>
       <c r="I20" s="20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>72 Years, 3 Months</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+        <v>72 Years, 4 Months</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -2233,10 +2231,10 @@
       </c>
       <c r="I21" s="20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29 Years, 4 Months</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+        <v>29 Years, 5 Months</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -2263,10 +2261,10 @@
       </c>
       <c r="I22" s="20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>37 Years, 7 Months</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+        <v>37 Years, 8 Months</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>75</v>
       </c>
@@ -2293,10 +2291,10 @@
       </c>
       <c r="I23" s="20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>37 Years, 10 Months</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+        <v>37 Years, 11 Months</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>77</v>
       </c>
@@ -2326,7 +2324,7 @@
         <v>50 Years, 6 Months</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>80</v>
       </c>
@@ -2356,7 +2354,7 @@
         <v>59 Years, 11 Months</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>83</v>
       </c>
@@ -2386,7 +2384,7 @@
         <v>58 Years, 6 Months</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -2416,7 +2414,7 @@
         <v>75 Years, 10 Months</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -2443,10 +2441,10 @@
       </c>
       <c r="I28" s="20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>61 Years, 7 Months</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+        <v>61 Years, 8 Months</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -2476,7 +2474,7 @@
         <v>73 Years, 7 Months</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -2506,7 +2504,7 @@
         <v>49 Years, 8 Months</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>96</v>
       </c>
@@ -2544,21 +2542,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O74"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.90625" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" customWidth="1"/>
-    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" customWidth="1"/>
-    <col min="12" max="12" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.90625" customWidth="1"/>
-    <col min="14" max="14" width="45.1796875" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.88671875" customWidth="1"/>
+    <col min="14" max="14" width="45.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>98</v>
       </c>
@@ -2581,7 +2579,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>104</v>
       </c>
@@ -2610,7 +2608,7 @@
       <c r="N2" s="14"/>
       <c r="O2" s="14"/>
     </row>
-    <row r="3" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>108</v>
       </c>
@@ -2642,7 +2640,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>112</v>
       </c>
@@ -2675,7 +2673,7 @@
       </c>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>116</v>
       </c>
@@ -2708,7 +2706,7 @@
       </c>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>120</v>
       </c>
@@ -2735,7 +2733,7 @@
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
-    <row r="7" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>123</v>
       </c>
@@ -2770,7 +2768,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>128</v>
       </c>
@@ -2805,7 +2803,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>132</v>
       </c>
@@ -2840,7 +2838,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>136</v>
       </c>
@@ -2875,7 +2873,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>139</v>
       </c>
@@ -2898,7 +2896,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>140</v>
       </c>
@@ -2921,7 +2919,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>141</v>
       </c>
@@ -2944,7 +2942,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>142</v>
       </c>
@@ -2967,7 +2965,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>143</v>
       </c>
@@ -2990,7 +2988,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>144</v>
       </c>
@@ -3013,7 +3011,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>145</v>
       </c>
@@ -3036,7 +3034,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>146</v>
       </c>
@@ -3059,7 +3057,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>147</v>
       </c>
@@ -3082,7 +3080,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>148</v>
       </c>
@@ -3105,7 +3103,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>149</v>
       </c>
@@ -3128,7 +3126,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>151</v>
       </c>
@@ -3151,7 +3149,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>152</v>
       </c>
@@ -3174,7 +3172,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>153</v>
       </c>
@@ -3197,7 +3195,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>154</v>
       </c>
@@ -3220,7 +3218,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>155</v>
       </c>
@@ -3243,7 +3241,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>156</v>
       </c>
@@ -3266,7 +3264,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>157</v>
       </c>
@@ -3289,7 +3287,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>158</v>
       </c>
@@ -3312,7 +3310,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>159</v>
       </c>
@@ -3335,7 +3333,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>160</v>
       </c>
@@ -3358,7 +3356,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>161</v>
       </c>
@@ -3381,7 +3379,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>163</v>
       </c>
@@ -3404,7 +3402,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>164</v>
       </c>
@@ -3427,7 +3425,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>165</v>
       </c>
@@ -3450,7 +3448,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>166</v>
       </c>
@@ -3473,7 +3471,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>167</v>
       </c>
@@ -3496,7 +3494,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>168</v>
       </c>
@@ -3519,7 +3517,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>169</v>
       </c>
@@ -3542,7 +3540,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>170</v>
       </c>
@@ -3565,7 +3563,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>171</v>
       </c>
@@ -3588,7 +3586,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>172</v>
       </c>
@@ -3611,7 +3609,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>173</v>
       </c>
@@ -3634,7 +3632,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>174</v>
       </c>
@@ -3657,7 +3655,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>175</v>
       </c>
@@ -3680,7 +3678,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>176</v>
       </c>
@@ -3703,7 +3701,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>177</v>
       </c>
@@ -3726,7 +3724,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>178</v>
       </c>
@@ -3749,7 +3747,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>179</v>
       </c>
@@ -3772,7 +3770,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>180</v>
       </c>
@@ -3795,7 +3793,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
         <v>181</v>
       </c>
@@ -3818,7 +3816,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>182</v>
       </c>
@@ -3841,7 +3839,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>183</v>
       </c>
@@ -3864,7 +3862,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>184</v>
       </c>
@@ -3887,7 +3885,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
         <v>185</v>
       </c>
@@ -3910,7 +3908,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>186</v>
       </c>
@@ -3933,7 +3931,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>187</v>
       </c>
@@ -3956,7 +3954,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>188</v>
       </c>
@@ -3979,7 +3977,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>189</v>
       </c>
@@ -4002,7 +4000,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>190</v>
       </c>
@@ -4025,7 +4023,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
         <v>191</v>
       </c>
@@ -4048,7 +4046,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>192</v>
       </c>
@@ -4071,7 +4069,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>193</v>
       </c>
@@ -4094,7 +4092,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>194</v>
       </c>
@@ -4117,7 +4115,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>195</v>
       </c>
@@ -4140,7 +4138,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
         <v>196</v>
       </c>
@@ -4163,7 +4161,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
         <v>197</v>
       </c>
@@ -4186,7 +4184,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>198</v>
       </c>
@@ -4209,7 +4207,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="69" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>199</v>
       </c>
@@ -4232,7 +4230,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="70" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
         <v>200</v>
       </c>
@@ -4255,7 +4253,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>201</v>
       </c>
@@ -4278,7 +4276,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="72" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>202</v>
       </c>
@@ -4301,7 +4299,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>203</v>
       </c>
@@ -4324,7 +4322,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
         <v>204</v>
       </c>
@@ -4360,16 +4358,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" customWidth="1"/>
-    <col min="2" max="2" width="70.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.21875" customWidth="1"/>
+    <col min="2" max="2" width="70.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>206</v>
       </c>
@@ -4386,7 +4384,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>211</v>
       </c>
@@ -4411,16 +4409,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
@@ -4440,7 +4438,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -4460,7 +4458,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -4480,7 +4478,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>133</v>
       </c>
@@ -4500,7 +4498,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -4520,7 +4518,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4540,7 +4538,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>150</v>
       </c>
@@ -4560,7 +4558,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -4580,7 +4578,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>50</v>
       </c>
@@ -4600,7 +4598,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>72</v>
       </c>
@@ -4620,7 +4618,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -4640,7 +4638,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -4660,7 +4658,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -4680,7 +4678,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -4700,7 +4698,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -4720,7 +4718,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>121</v>
       </c>
@@ -4740,7 +4738,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -4760,7 +4758,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -4780,7 +4778,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -4808,16 +4806,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7265625" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4834,7 +4832,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4851,7 +4849,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4868,7 +4866,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4885,7 +4883,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -4902,7 +4900,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -4919,7 +4917,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4936,7 +4934,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -4953,7 +4951,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -4970,7 +4968,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -4987,7 +4985,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -5004,7 +5002,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>48</v>
       </c>
@@ -5021,7 +5019,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -5038,7 +5036,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -5055,7 +5053,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -5072,7 +5070,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -5089,7 +5087,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -5106,7 +5104,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -5123,7 +5121,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -5140,7 +5138,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -5157,7 +5155,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -5174,7 +5172,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -5191,7 +5189,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>75</v>
       </c>
@@ -5208,7 +5206,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>77</v>
       </c>
@@ -5225,7 +5223,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>80</v>
       </c>
@@ -5242,7 +5240,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>83</v>
       </c>
@@ -5259,7 +5257,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -5276,7 +5274,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -5293,7 +5291,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -5310,7 +5308,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -5327,7 +5325,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>96</v>
       </c>
@@ -5352,23 +5350,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.54296875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="83.36328125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="17.26953125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19.81640625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="16.453125" style="9" customWidth="1"/>
-    <col min="8" max="9" width="8.7265625" style="9"/>
-    <col min="10" max="10" width="16.453125" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="61.453125" style="9" customWidth="1"/>
-    <col min="12" max="12" width="17.81640625" style="9" customWidth="1"/>
-    <col min="13" max="16384" width="8.7265625" style="9"/>
+    <col min="1" max="1" width="10.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="83.33203125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="9" customWidth="1"/>
+    <col min="8" max="9" width="8.77734375" style="9"/>
+    <col min="10" max="10" width="16.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="61.44140625" style="9" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" style="9" customWidth="1"/>
+    <col min="13" max="16384" width="8.77734375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>260</v>
       </c>
@@ -5392,7 +5390,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>266</v>
       </c>
@@ -5421,7 +5419,7 @@
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
     </row>
-    <row r="3" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>271</v>
       </c>
@@ -5454,7 +5452,7 @@
       </c>
       <c r="M3" s="14"/>
     </row>
-    <row r="4" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>276</v>
       </c>
@@ -5487,19 +5485,19 @@
       </c>
       <c r="M4" s="14"/>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J7" s="16" t="s">
         <v>124</v>
       </c>
@@ -5513,7 +5511,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J8" s="16">
         <v>77063</v>
       </c>
@@ -5527,7 +5525,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J9" s="16">
         <v>77067</v>
       </c>
@@ -5541,7 +5539,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J10" s="16"/>
       <c r="K10" s="18"/>
       <c r="L10" s="17"/>
@@ -5560,16 +5558,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>281</v>
       </c>
@@ -5589,7 +5587,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>284</v>
       </c>
@@ -5606,7 +5604,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>287</v>
       </c>
@@ -5623,7 +5621,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>289</v>
       </c>
@@ -5640,7 +5638,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>292</v>
       </c>
@@ -5657,7 +5655,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>293</v>
       </c>
@@ -5674,7 +5672,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>294</v>
       </c>
@@ -5691,7 +5689,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>295</v>
       </c>
@@ -5708,7 +5706,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>296</v>
       </c>
@@ -5728,7 +5726,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>300</v>
       </c>
@@ -5748,7 +5746,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>301</v>
       </c>
@@ -5776,17 +5774,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.453125" customWidth="1"/>
+    <col min="5" max="6" width="12.44140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>303</v>
       </c>
@@ -5809,7 +5807,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>306</v>
       </c>
@@ -5832,7 +5830,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>311</v>
       </c>
@@ -5855,7 +5853,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>316</v>
       </c>
@@ -5878,7 +5876,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>319</v>
       </c>
@@ -5901,7 +5899,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>320</v>
       </c>
@@ -5924,7 +5922,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>321</v>
       </c>
@@ -5947,7 +5945,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>322</v>
       </c>
